--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2023.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2023.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="695">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -1195,15 +1195,6 @@
     <t xml:space="preserve">Andacollo</t>
   </si>
   <si>
-    <t xml:space="preserve">Arica y Parinacota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arica</t>
-  </si>
-  <si>
     <t xml:space="preserve">4102</t>
   </si>
   <si>
@@ -2065,7 +2056,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:50</t>
+    <t xml:space="preserve">2026-09-07 12:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2477,7 +2468,7 @@
   <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
@@ -8380,16 +8371,16 @@
         <v>2023</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C185" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D185" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="D185" s="2" t="s">
-        <v>393</v>
-      </c>
       <c r="E185" s="2" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>385</v>
@@ -8401,7 +8392,7 @@
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>48.01</v>
+        <v>47.12</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>16</v>
@@ -8412,16 +8403,16 @@
         <v>2023</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>385</v>
@@ -8433,7 +8424,7 @@
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>47.12</v>
+        <v>47.03</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>16</v>
@@ -8444,10 +8435,10 @@
         <v>2023</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>396</v>
@@ -8465,7 +8456,7 @@
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>47.03</v>
+        <v>46.59</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>16</v>
@@ -8476,7 +8467,7 @@
         <v>2023</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>398</v>
@@ -8497,7 +8488,7 @@
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>46.59</v>
+        <v>46.4</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>16</v>
@@ -8508,16 +8499,16 @@
         <v>2023</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C189" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D189" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="D189" s="2" t="s">
-        <v>402</v>
-      </c>
       <c r="E189" s="2" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>385</v>
@@ -8529,7 +8520,7 @@
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>46.4</v>
+        <v>46.39</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>16</v>
@@ -8540,16 +8531,16 @@
         <v>2023</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>385</v>
@@ -8561,7 +8552,7 @@
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>46.39</v>
+        <v>45.99</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>16</v>
@@ -8578,10 +8569,10 @@
         <v>382</v>
       </c>
       <c r="D191" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E191" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="E191" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>385</v>
@@ -8593,7 +8584,7 @@
         <v>15</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>45.99</v>
+        <v>45.41</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>16</v>
@@ -8604,16 +8595,16 @@
         <v>2023</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="D192" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E192" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="E192" s="2" t="s">
-        <v>408</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>385</v>
@@ -8625,7 +8616,7 @@
         <v>15</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>45.41</v>
+        <v>45.22</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>16</v>
@@ -8636,16 +8627,16 @@
         <v>2023</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="D193" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E193" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="E193" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>385</v>
@@ -8657,7 +8648,7 @@
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>45.22</v>
+        <v>43.87</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>16</v>
@@ -8674,10 +8665,10 @@
         <v>382</v>
       </c>
       <c r="D194" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E194" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="E194" s="2" t="s">
-        <v>412</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>385</v>
@@ -8689,7 +8680,7 @@
         <v>15</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>43.87</v>
+        <v>43.39</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>16</v>
@@ -8706,10 +8697,10 @@
         <v>382</v>
       </c>
       <c r="D195" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E195" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="E195" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>385</v>
@@ -8721,7 +8712,7 @@
         <v>15</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>43.39</v>
+        <v>43.23</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>16</v>
@@ -8732,16 +8723,16 @@
         <v>2023</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D196" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E196" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>416</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>385</v>
@@ -8753,7 +8744,7 @@
         <v>15</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>43.23</v>
+        <v>43.03</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>16</v>
@@ -8770,10 +8761,10 @@
         <v>387</v>
       </c>
       <c r="D197" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E197" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>418</v>
       </c>
       <c r="F197" s="2" t="s">
         <v>385</v>
@@ -8785,7 +8776,7 @@
         <v>15</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>43.03</v>
+        <v>42.6</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>16</v>
@@ -8796,16 +8787,16 @@
         <v>2023</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="D198" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E198" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="E198" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>385</v>
@@ -8817,7 +8808,7 @@
         <v>15</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>42.6</v>
+        <v>42.3</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>16</v>
@@ -8828,16 +8819,16 @@
         <v>2023</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="D199" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E199" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="E199" s="2" t="s">
-        <v>422</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>385</v>
@@ -8849,7 +8840,7 @@
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>42.3</v>
+        <v>41.78</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>16</v>
@@ -8860,16 +8851,16 @@
         <v>2023</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="D200" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E200" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="E200" s="2" t="s">
-        <v>424</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>385</v>
@@ -8881,7 +8872,7 @@
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>41.78</v>
+        <v>41.13</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>16</v>
@@ -8892,16 +8883,16 @@
         <v>2023</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="D201" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E201" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>426</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>385</v>
@@ -8913,7 +8904,7 @@
         <v>15</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>41.13</v>
+        <v>41.12</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>16</v>
@@ -8924,16 +8915,16 @@
         <v>2023</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D202" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E202" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>428</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>385</v>
@@ -8945,7 +8936,7 @@
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>41.12</v>
+        <v>40.29</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>16</v>
@@ -8962,10 +8953,10 @@
         <v>387</v>
       </c>
       <c r="D203" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E203" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="E203" s="2" t="s">
-        <v>430</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>385</v>
@@ -8977,7 +8968,7 @@
         <v>15</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>40.29</v>
+        <v>39.56</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>16</v>
@@ -8988,16 +8979,16 @@
         <v>2023</v>
       </c>
       <c r="B204" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D204" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E204" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>385</v>
@@ -9009,7 +9000,7 @@
         <v>15</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>39.56</v>
+        <v>38.42</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>16</v>
@@ -9026,10 +9017,10 @@
         <v>382</v>
       </c>
       <c r="D205" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E205" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="E205" s="2" t="s">
-        <v>434</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>385</v>
@@ -9041,7 +9032,7 @@
         <v>15</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>38.42</v>
+        <v>38.08</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>16</v>
@@ -9052,16 +9043,16 @@
         <v>2023</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="D206" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E206" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>385</v>
@@ -9073,7 +9064,7 @@
         <v>15</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>38.08</v>
+        <v>36.84</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>16</v>
@@ -9084,16 +9075,16 @@
         <v>2023</v>
       </c>
       <c r="B207" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="D207" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E207" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>438</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>385</v>
@@ -9105,7 +9096,7 @@
         <v>15</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>36.84</v>
+        <v>36.77</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>16</v>
@@ -9116,16 +9107,16 @@
         <v>2023</v>
       </c>
       <c r="B208" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="D208" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E208" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>385</v>
@@ -9137,7 +9128,7 @@
         <v>15</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>36.77</v>
+        <v>36.4</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>16</v>
@@ -9148,16 +9139,16 @@
         <v>2023</v>
       </c>
       <c r="B209" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="D209" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E209" s="2" t="s">
         <v>441</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>442</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>385</v>
@@ -9169,7 +9160,7 @@
         <v>15</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>36.4</v>
+        <v>36.36</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>16</v>
@@ -9180,16 +9171,16 @@
         <v>2023</v>
       </c>
       <c r="B210" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="D210" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="E210" s="2" t="s">
         <v>443</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>444</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>385</v>
@@ -9201,7 +9192,7 @@
         <v>15</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>36.36</v>
+        <v>36.27</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>16</v>
@@ -9212,16 +9203,16 @@
         <v>2023</v>
       </c>
       <c r="B211" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="D211" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E211" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>446</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>385</v>
@@ -9233,7 +9224,7 @@
         <v>15</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>36.27</v>
+        <v>36.19</v>
       </c>
       <c r="J211" s="2" t="s">
         <v>16</v>
@@ -9244,16 +9235,16 @@
         <v>2023</v>
       </c>
       <c r="B212" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="D212" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E212" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>385</v>
@@ -9265,7 +9256,7 @@
         <v>15</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>36.19</v>
+        <v>36.05</v>
       </c>
       <c r="J212" s="2" t="s">
         <v>16</v>
@@ -9276,16 +9267,16 @@
         <v>2023</v>
       </c>
       <c r="B213" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="D213" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E213" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>385</v>
@@ -9297,7 +9288,7 @@
         <v>15</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>36.05</v>
+        <v>35.44</v>
       </c>
       <c r="J213" s="2" t="s">
         <v>16</v>
@@ -9311,13 +9302,13 @@
         <v>2</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D214" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E214" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>452</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>385</v>
@@ -9329,7 +9320,7 @@
         <v>15</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>35.44</v>
+        <v>34.91</v>
       </c>
       <c r="J214" s="2" t="s">
         <v>16</v>
@@ -9340,16 +9331,16 @@
         <v>2023</v>
       </c>
       <c r="B215" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="D215" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E215" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="E215" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>385</v>
@@ -9361,7 +9352,7 @@
         <v>15</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>34.91</v>
+        <v>31.8</v>
       </c>
       <c r="J215" s="2" t="s">
         <v>16</v>
@@ -9372,16 +9363,16 @@
         <v>2023</v>
       </c>
       <c r="B216" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="D216" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="E216" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>456</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>385</v>
@@ -9393,7 +9384,7 @@
         <v>15</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>31.8</v>
+        <v>29.8</v>
       </c>
       <c r="J216" s="2" t="s">
         <v>16</v>
@@ -9407,13 +9398,13 @@
         <v>1</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D217" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E217" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>458</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>385</v>
@@ -9425,7 +9416,7 @@
         <v>15</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>29.8</v>
+        <v>29.53</v>
       </c>
       <c r="J217" s="2" t="s">
         <v>16</v>
@@ -9436,16 +9427,16 @@
         <v>2023</v>
       </c>
       <c r="B218" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="D218" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E218" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>385</v>
@@ -9457,7 +9448,7 @@
         <v>15</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>29.53</v>
+        <v>26.28</v>
       </c>
       <c r="J218" s="2" t="s">
         <v>16</v>
@@ -9468,10 +9459,10 @@
         <v>2023</v>
       </c>
       <c r="B219" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>382</v>
+        <v>460</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>461</v>
@@ -9480,16 +9471,16 @@
         <v>462</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>385</v>
+        <v>463</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>386</v>
+        <v>464</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>26.28</v>
+        <v>56.84</v>
       </c>
       <c r="J219" s="2" t="s">
         <v>16</v>
@@ -9503,25 +9494,25 @@
         <v>8</v>
       </c>
       <c r="C220" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="F220" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D220" s="2" t="s">
+      <c r="G220" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="E220" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="G220" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>56.84</v>
+        <v>56.58</v>
       </c>
       <c r="J220" s="2" t="s">
         <v>16</v>
@@ -9535,25 +9526,25 @@
         <v>8</v>
       </c>
       <c r="C221" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="F221" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D221" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="E221" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F221" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G221" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>56.58</v>
+        <v>54.94</v>
       </c>
       <c r="J221" s="2" t="s">
         <v>16</v>
@@ -9567,25 +9558,25 @@
         <v>8</v>
       </c>
       <c r="C222" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="F222" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D222" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F222" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G222" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>54.94</v>
+        <v>54.84</v>
       </c>
       <c r="J222" s="2" t="s">
         <v>16</v>
@@ -9596,10 +9587,10 @@
         <v>2023</v>
       </c>
       <c r="B223" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>472</v>
@@ -9608,16 +9599,16 @@
         <v>473</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>54.84</v>
+        <v>53.02</v>
       </c>
       <c r="J223" s="2" t="s">
         <v>16</v>
@@ -9628,28 +9619,28 @@
         <v>2023</v>
       </c>
       <c r="B224" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C224" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D224" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D224" s="2" t="s">
+      <c r="E224" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="E224" s="2" t="s">
-        <v>476</v>
-      </c>
       <c r="F224" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>53.02</v>
+        <v>52.87</v>
       </c>
       <c r="J224" s="2" t="s">
         <v>16</v>
@@ -9660,10 +9651,10 @@
         <v>2023</v>
       </c>
       <c r="B225" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>477</v>
@@ -9672,16 +9663,16 @@
         <v>478</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>52.87</v>
+        <v>51.41</v>
       </c>
       <c r="J225" s="2" t="s">
         <v>16</v>
@@ -9692,28 +9683,28 @@
         <v>2023</v>
       </c>
       <c r="B226" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C226" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D226" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="D226" s="2" t="s">
+      <c r="E226" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="E226" s="2" t="s">
-        <v>481</v>
-      </c>
       <c r="F226" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>51.41</v>
+        <v>50.8</v>
       </c>
       <c r="J226" s="2" t="s">
         <v>16</v>
@@ -9724,10 +9715,10 @@
         <v>2023</v>
       </c>
       <c r="B227" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>482</v>
@@ -9736,16 +9727,16 @@
         <v>483</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>50.8</v>
+        <v>50.47</v>
       </c>
       <c r="J227" s="2" t="s">
         <v>16</v>
@@ -9756,28 +9747,28 @@
         <v>2023</v>
       </c>
       <c r="B228" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C228" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D228" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="D228" s="2" t="s">
+      <c r="E228" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="E228" s="2" t="s">
-        <v>486</v>
-      </c>
       <c r="F228" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>50.47</v>
+        <v>50.06</v>
       </c>
       <c r="J228" s="2" t="s">
         <v>16</v>
@@ -9791,25 +9782,25 @@
         <v>8</v>
       </c>
       <c r="C229" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="F229" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D229" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="E229" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="F229" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G229" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>50.06</v>
+        <v>49.5</v>
       </c>
       <c r="J229" s="2" t="s">
         <v>16</v>
@@ -9823,25 +9814,25 @@
         <v>8</v>
       </c>
       <c r="C230" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="F230" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D230" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E230" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G230" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>49.5</v>
+        <v>49.18</v>
       </c>
       <c r="J230" s="2" t="s">
         <v>16</v>
@@ -9855,25 +9846,25 @@
         <v>8</v>
       </c>
       <c r="C231" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="F231" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D231" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="F231" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G231" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>49.18</v>
+        <v>49</v>
       </c>
       <c r="J231" s="2" t="s">
         <v>16</v>
@@ -9887,25 +9878,25 @@
         <v>8</v>
       </c>
       <c r="C232" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="F232" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D232" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="E232" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G232" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>49</v>
+        <v>48.74</v>
       </c>
       <c r="J232" s="2" t="s">
         <v>16</v>
@@ -9916,28 +9907,28 @@
         <v>2023</v>
       </c>
       <c r="B233" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C233" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="F233" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D233" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="E233" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="F233" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G233" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>48.74</v>
+        <v>48.19</v>
       </c>
       <c r="J233" s="2" t="s">
         <v>16</v>
@@ -9948,28 +9939,28 @@
         <v>2023</v>
       </c>
       <c r="B234" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>484</v>
+        <v>460</v>
       </c>
       <c r="D234" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E234" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="E234" s="2" t="s">
-        <v>498</v>
-      </c>
       <c r="F234" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>48.19</v>
+        <v>47.68</v>
       </c>
       <c r="J234" s="2" t="s">
         <v>16</v>
@@ -9983,25 +9974,25 @@
         <v>8</v>
       </c>
       <c r="C235" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="F235" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D235" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G235" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>47.68</v>
+        <v>47.57</v>
       </c>
       <c r="J235" s="2" t="s">
         <v>16</v>
@@ -10012,28 +10003,28 @@
         <v>2023</v>
       </c>
       <c r="B236" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C236" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="F236" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D236" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="E236" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G236" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>47.57</v>
+        <v>47.1</v>
       </c>
       <c r="J236" s="2" t="s">
         <v>16</v>
@@ -10044,28 +10035,28 @@
         <v>2023</v>
       </c>
       <c r="B237" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="D237" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E237" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="E237" s="2" t="s">
-        <v>504</v>
-      </c>
       <c r="F237" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>47.1</v>
+        <v>47.08</v>
       </c>
       <c r="J237" s="2" t="s">
         <v>16</v>
@@ -10079,25 +10070,25 @@
         <v>8</v>
       </c>
       <c r="C238" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="F238" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D238" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="E238" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="F238" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G238" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>47.08</v>
+        <v>46</v>
       </c>
       <c r="J238" s="2" t="s">
         <v>16</v>
@@ -10111,25 +10102,25 @@
         <v>8</v>
       </c>
       <c r="C239" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="F239" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D239" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="F239" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G239" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>46</v>
+        <v>45.85</v>
       </c>
       <c r="J239" s="2" t="s">
         <v>16</v>
@@ -10140,28 +10131,28 @@
         <v>2023</v>
       </c>
       <c r="B240" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C240" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="F240" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D240" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="F240" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G240" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>45.85</v>
+        <v>45.63</v>
       </c>
       <c r="J240" s="2" t="s">
         <v>16</v>
@@ -10172,28 +10163,28 @@
         <v>2023</v>
       </c>
       <c r="B241" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="D241" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E241" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="E241" s="2" t="s">
-        <v>512</v>
-      </c>
       <c r="F241" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>45.63</v>
+        <v>45.43</v>
       </c>
       <c r="J241" s="2" t="s">
         <v>16</v>
@@ -10204,28 +10195,28 @@
         <v>2023</v>
       </c>
       <c r="B242" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C242" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="F242" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D242" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="E242" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="F242" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G242" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>45.43</v>
+        <v>45.27</v>
       </c>
       <c r="J242" s="2" t="s">
         <v>16</v>
@@ -10239,25 +10230,25 @@
         <v>14</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D243" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="E243" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="E243" s="2" t="s">
-        <v>516</v>
-      </c>
       <c r="F243" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>45.27</v>
+        <v>45.23</v>
       </c>
       <c r="J243" s="2" t="s">
         <v>16</v>
@@ -10268,28 +10259,28 @@
         <v>2023</v>
       </c>
       <c r="B244" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>484</v>
+        <v>460</v>
       </c>
       <c r="D244" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="E244" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="E244" s="2" t="s">
-        <v>518</v>
-      </c>
       <c r="F244" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>45.23</v>
+        <v>45.14</v>
       </c>
       <c r="J244" s="2" t="s">
         <v>16</v>
@@ -10303,25 +10294,25 @@
         <v>8</v>
       </c>
       <c r="C245" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F245" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D245" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="F245" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G245" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>45.14</v>
+        <v>45.13</v>
       </c>
       <c r="J245" s="2" t="s">
         <v>16</v>
@@ -10335,25 +10326,25 @@
         <v>8</v>
       </c>
       <c r="C246" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="F246" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D246" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="F246" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G246" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>45.13</v>
+        <v>44.81</v>
       </c>
       <c r="J246" s="2" t="s">
         <v>16</v>
@@ -10364,28 +10355,28 @@
         <v>2023</v>
       </c>
       <c r="B247" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C247" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="F247" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D247" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F247" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G247" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>44.81</v>
+        <v>44.78</v>
       </c>
       <c r="J247" s="2" t="s">
         <v>16</v>
@@ -10396,28 +10387,28 @@
         <v>2023</v>
       </c>
       <c r="B248" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="D248" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E248" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="E248" s="2" t="s">
-        <v>526</v>
-      </c>
       <c r="F248" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>44.78</v>
+        <v>44.63</v>
       </c>
       <c r="J248" s="2" t="s">
         <v>16</v>
@@ -10428,28 +10419,28 @@
         <v>2023</v>
       </c>
       <c r="B249" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C249" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F249" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D249" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="E249" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F249" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G249" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>44.63</v>
+        <v>44.14</v>
       </c>
       <c r="J249" s="2" t="s">
         <v>16</v>
@@ -10460,28 +10451,28 @@
         <v>2023</v>
       </c>
       <c r="B250" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="D250" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E250" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="E250" s="2" t="s">
-        <v>530</v>
-      </c>
       <c r="F250" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>44.14</v>
+        <v>44</v>
       </c>
       <c r="J250" s="2" t="s">
         <v>16</v>
@@ -10492,28 +10483,28 @@
         <v>2023</v>
       </c>
       <c r="B251" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C251" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="F251" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D251" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="E251" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="F251" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G251" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>44</v>
+        <v>43.95</v>
       </c>
       <c r="J251" s="2" t="s">
         <v>16</v>
@@ -10524,28 +10515,28 @@
         <v>2023</v>
       </c>
       <c r="B252" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D252" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E252" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="E252" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="F252" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>43.95</v>
+        <v>43.81</v>
       </c>
       <c r="J252" s="2" t="s">
         <v>16</v>
@@ -10556,28 +10547,28 @@
         <v>2023</v>
       </c>
       <c r="B253" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="D253" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E253" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="E253" s="2" t="s">
-        <v>536</v>
-      </c>
       <c r="F253" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>43.81</v>
+        <v>43.76</v>
       </c>
       <c r="J253" s="2" t="s">
         <v>16</v>
@@ -10591,25 +10582,25 @@
         <v>8</v>
       </c>
       <c r="C254" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="F254" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D254" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G254" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>43.76</v>
+        <v>43.6</v>
       </c>
       <c r="J254" s="2" t="s">
         <v>16</v>
@@ -10620,28 +10611,28 @@
         <v>2023</v>
       </c>
       <c r="B255" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C255" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="F255" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D255" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="E255" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="F255" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G255" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>43.6</v>
+        <v>43.36</v>
       </c>
       <c r="J255" s="2" t="s">
         <v>16</v>
@@ -10652,28 +10643,28 @@
         <v>2023</v>
       </c>
       <c r="B256" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="D256" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="E256" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="E256" s="2" t="s">
-        <v>542</v>
-      </c>
       <c r="F256" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>43.36</v>
+        <v>43.3</v>
       </c>
       <c r="J256" s="2" t="s">
         <v>16</v>
@@ -10684,28 +10675,28 @@
         <v>2023</v>
       </c>
       <c r="B257" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C257" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="F257" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D257" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="E257" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="F257" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G257" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>43.3</v>
+        <v>43.09</v>
       </c>
       <c r="J257" s="2" t="s">
         <v>16</v>
@@ -10716,22 +10707,22 @@
         <v>2023</v>
       </c>
       <c r="B258" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="D258" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E258" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="E258" s="2" t="s">
-        <v>546</v>
-      </c>
       <c r="F258" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>15</v>
@@ -10751,25 +10742,25 @@
         <v>10</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D259" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="E259" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="E259" s="2" t="s">
-        <v>548</v>
-      </c>
       <c r="F259" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>43.09</v>
+        <v>42.92</v>
       </c>
       <c r="J259" s="2" t="s">
         <v>16</v>
@@ -10780,28 +10771,28 @@
         <v>2023</v>
       </c>
       <c r="B260" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D260" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E260" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="E260" s="2" t="s">
-        <v>550</v>
-      </c>
       <c r="F260" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>42.92</v>
+        <v>42.87</v>
       </c>
       <c r="J260" s="2" t="s">
         <v>16</v>
@@ -10812,28 +10803,28 @@
         <v>2023</v>
       </c>
       <c r="B261" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="D261" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E261" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="E261" s="2" t="s">
-        <v>552</v>
-      </c>
       <c r="F261" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>42.87</v>
+        <v>42.7</v>
       </c>
       <c r="J261" s="2" t="s">
         <v>16</v>
@@ -10844,28 +10835,28 @@
         <v>2023</v>
       </c>
       <c r="B262" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="D262" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="E262" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="E262" s="2" t="s">
-        <v>554</v>
-      </c>
       <c r="F262" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>42.7</v>
+        <v>42.36</v>
       </c>
       <c r="J262" s="2" t="s">
         <v>16</v>
@@ -10876,28 +10867,28 @@
         <v>2023</v>
       </c>
       <c r="B263" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>484</v>
+        <v>460</v>
       </c>
       <c r="D263" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="E263" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="E263" s="2" t="s">
-        <v>556</v>
-      </c>
       <c r="F263" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H263" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>42.36</v>
+        <v>41.89</v>
       </c>
       <c r="J263" s="2" t="s">
         <v>16</v>
@@ -10908,28 +10899,28 @@
         <v>2023</v>
       </c>
       <c r="B264" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C264" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="F264" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D264" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="E264" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="F264" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G264" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>41.89</v>
+        <v>41.73</v>
       </c>
       <c r="J264" s="2" t="s">
         <v>16</v>
@@ -10943,25 +10934,25 @@
         <v>9</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D265" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="E265" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="E265" s="2" t="s">
-        <v>560</v>
-      </c>
       <c r="F265" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>41.73</v>
+        <v>41.65</v>
       </c>
       <c r="J265" s="2" t="s">
         <v>16</v>
@@ -10972,28 +10963,28 @@
         <v>2023</v>
       </c>
       <c r="B266" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D266" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E266" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="E266" s="2" t="s">
-        <v>562</v>
-      </c>
       <c r="F266" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>41.65</v>
+        <v>41.57</v>
       </c>
       <c r="J266" s="2" t="s">
         <v>16</v>
@@ -11004,28 +10995,28 @@
         <v>2023</v>
       </c>
       <c r="B267" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>484</v>
+        <v>460</v>
       </c>
       <c r="D267" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="E267" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="E267" s="2" t="s">
-        <v>564</v>
-      </c>
       <c r="F267" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>41.57</v>
+        <v>41.48</v>
       </c>
       <c r="J267" s="2" t="s">
         <v>16</v>
@@ -11036,28 +11027,28 @@
         <v>2023</v>
       </c>
       <c r="B268" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C268" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="F268" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D268" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="E268" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="F268" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G268" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I268" s="2" t="n">
-        <v>41.48</v>
+        <v>41.44</v>
       </c>
       <c r="J268" s="2" t="s">
         <v>16</v>
@@ -11068,28 +11059,28 @@
         <v>2023</v>
       </c>
       <c r="B269" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D269" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="E269" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="E269" s="2" t="s">
-        <v>568</v>
-      </c>
       <c r="F269" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>41.44</v>
+        <v>41.41</v>
       </c>
       <c r="J269" s="2" t="s">
         <v>16</v>
@@ -11103,25 +11094,25 @@
         <v>9</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D270" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="E270" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="E270" s="2" t="s">
-        <v>570</v>
-      </c>
       <c r="F270" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>41.41</v>
+        <v>41.25</v>
       </c>
       <c r="J270" s="2" t="s">
         <v>16</v>
@@ -11132,28 +11123,28 @@
         <v>2023</v>
       </c>
       <c r="B271" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="D271" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E271" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="E271" s="2" t="s">
-        <v>572</v>
-      </c>
       <c r="F271" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>41.25</v>
+        <v>41.22</v>
       </c>
       <c r="J271" s="2" t="s">
         <v>16</v>
@@ -11164,28 +11155,28 @@
         <v>2023</v>
       </c>
       <c r="B272" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="D272" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E272" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="E272" s="2" t="s">
-        <v>574</v>
-      </c>
       <c r="F272" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>41.22</v>
+        <v>41.16</v>
       </c>
       <c r="J272" s="2" t="s">
         <v>16</v>
@@ -11196,28 +11187,28 @@
         <v>2023</v>
       </c>
       <c r="B273" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C273" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="F273" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D273" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="E273" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="F273" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G273" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>41.16</v>
+        <v>40.94</v>
       </c>
       <c r="J273" s="2" t="s">
         <v>16</v>
@@ -11228,28 +11219,28 @@
         <v>2023</v>
       </c>
       <c r="B274" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="D274" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="E274" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="E274" s="2" t="s">
-        <v>578</v>
-      </c>
       <c r="F274" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>40.94</v>
+        <v>40.93</v>
       </c>
       <c r="J274" s="2" t="s">
         <v>16</v>
@@ -11260,28 +11251,28 @@
         <v>2023</v>
       </c>
       <c r="B275" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D275" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="E275" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="E275" s="2" t="s">
-        <v>580</v>
-      </c>
       <c r="F275" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>40.93</v>
+        <v>40.79</v>
       </c>
       <c r="J275" s="2" t="s">
         <v>16</v>
@@ -11292,28 +11283,28 @@
         <v>2023</v>
       </c>
       <c r="B276" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D276" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="E276" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="E276" s="2" t="s">
-        <v>582</v>
-      </c>
       <c r="F276" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>40.79</v>
+        <v>40.74</v>
       </c>
       <c r="J276" s="2" t="s">
         <v>16</v>
@@ -11324,28 +11315,28 @@
         <v>2023</v>
       </c>
       <c r="B277" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>484</v>
+        <v>460</v>
       </c>
       <c r="D277" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E277" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="E277" s="2" t="s">
-        <v>584</v>
-      </c>
       <c r="F277" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>40.74</v>
+        <v>40.58</v>
       </c>
       <c r="J277" s="2" t="s">
         <v>16</v>
@@ -11359,25 +11350,25 @@
         <v>8</v>
       </c>
       <c r="C278" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="E278" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="F278" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D278" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="F278" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G278" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>40.58</v>
+        <v>40.55</v>
       </c>
       <c r="J278" s="2" t="s">
         <v>16</v>
@@ -11388,28 +11379,28 @@
         <v>2023</v>
       </c>
       <c r="B279" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C279" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="E279" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="F279" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D279" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="E279" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="F279" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G279" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>40.55</v>
+        <v>40.32</v>
       </c>
       <c r="J279" s="2" t="s">
         <v>16</v>
@@ -11420,28 +11411,28 @@
         <v>2023</v>
       </c>
       <c r="B280" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="D280" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="E280" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="E280" s="2" t="s">
-        <v>590</v>
-      </c>
       <c r="F280" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>40.32</v>
+        <v>40.02</v>
       </c>
       <c r="J280" s="2" t="s">
         <v>16</v>
@@ -11452,28 +11443,28 @@
         <v>2023</v>
       </c>
       <c r="B281" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="D281" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="E281" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="E281" s="2" t="s">
-        <v>592</v>
-      </c>
       <c r="F281" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I281" s="2" t="n">
-        <v>40.02</v>
+        <v>39.75</v>
       </c>
       <c r="J281" s="2" t="s">
         <v>16</v>
@@ -11484,28 +11475,28 @@
         <v>2023</v>
       </c>
       <c r="B282" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D282" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="E282" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="E282" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="F282" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I282" s="2" t="n">
-        <v>39.75</v>
+        <v>39.64</v>
       </c>
       <c r="J282" s="2" t="s">
         <v>16</v>
@@ -11516,28 +11507,28 @@
         <v>2023</v>
       </c>
       <c r="B283" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="D283" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="E283" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="E283" s="2" t="s">
-        <v>596</v>
-      </c>
       <c r="F283" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>39.64</v>
+        <v>39.31</v>
       </c>
       <c r="J283" s="2" t="s">
         <v>16</v>
@@ -11548,28 +11539,28 @@
         <v>2023</v>
       </c>
       <c r="B284" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="D284" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="E284" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="E284" s="2" t="s">
-        <v>598</v>
-      </c>
       <c r="F284" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>39.31</v>
+        <v>38.99</v>
       </c>
       <c r="J284" s="2" t="s">
         <v>16</v>
@@ -11583,25 +11574,25 @@
         <v>9</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D285" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="E285" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="E285" s="2" t="s">
-        <v>600</v>
-      </c>
       <c r="F285" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>38.99</v>
+        <v>38.7</v>
       </c>
       <c r="J285" s="2" t="s">
         <v>16</v>
@@ -11612,28 +11603,28 @@
         <v>2023</v>
       </c>
       <c r="B286" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="D286" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E286" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="E286" s="2" t="s">
-        <v>602</v>
-      </c>
       <c r="F286" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>38.7</v>
+        <v>38.68</v>
       </c>
       <c r="J286" s="2" t="s">
         <v>16</v>
@@ -11647,25 +11638,25 @@
         <v>10</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D287" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="E287" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="E287" s="2" t="s">
-        <v>604</v>
-      </c>
       <c r="F287" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>38.68</v>
+        <v>38.61</v>
       </c>
       <c r="J287" s="2" t="s">
         <v>16</v>
@@ -11676,28 +11667,28 @@
         <v>2023</v>
       </c>
       <c r="B288" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="D288" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="E288" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="E288" s="2" t="s">
-        <v>606</v>
-      </c>
       <c r="F288" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>38.61</v>
+        <v>38.54</v>
       </c>
       <c r="J288" s="2" t="s">
         <v>16</v>
@@ -11708,28 +11699,28 @@
         <v>2023</v>
       </c>
       <c r="B289" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C289" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="F289" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D289" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="E289" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="F289" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G289" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I289" s="2" t="n">
-        <v>38.54</v>
+        <v>38.33</v>
       </c>
       <c r="J289" s="2" t="s">
         <v>16</v>
@@ -11743,25 +11734,25 @@
         <v>10</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D290" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="E290" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="E290" s="2" t="s">
-        <v>610</v>
-      </c>
       <c r="F290" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>38.33</v>
+        <v>38.27</v>
       </c>
       <c r="J290" s="2" t="s">
         <v>16</v>
@@ -11772,28 +11763,28 @@
         <v>2023</v>
       </c>
       <c r="B291" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D291" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="E291" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="E291" s="2" t="s">
-        <v>612</v>
-      </c>
       <c r="F291" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I291" s="2" t="n">
-        <v>38.27</v>
+        <v>38.24</v>
       </c>
       <c r="J291" s="2" t="s">
         <v>16</v>
@@ -11804,28 +11795,28 @@
         <v>2023</v>
       </c>
       <c r="B292" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="D292" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="E292" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="E292" s="2" t="s">
-        <v>614</v>
-      </c>
       <c r="F292" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>38.24</v>
+        <v>38.09</v>
       </c>
       <c r="J292" s="2" t="s">
         <v>16</v>
@@ -11836,28 +11827,28 @@
         <v>2023</v>
       </c>
       <c r="B293" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D293" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="E293" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="E293" s="2" t="s">
-        <v>616</v>
-      </c>
       <c r="F293" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I293" s="2" t="n">
-        <v>38.09</v>
+        <v>38.03</v>
       </c>
       <c r="J293" s="2" t="s">
         <v>16</v>
@@ -11871,25 +11862,25 @@
         <v>9</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D294" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="E294" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="E294" s="2" t="s">
-        <v>618</v>
-      </c>
       <c r="F294" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>38.03</v>
+        <v>37.85</v>
       </c>
       <c r="J294" s="2" t="s">
         <v>16</v>
@@ -11903,25 +11894,25 @@
         <v>9</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D295" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="E295" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="E295" s="2" t="s">
-        <v>620</v>
-      </c>
       <c r="F295" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>37.85</v>
+        <v>37.76</v>
       </c>
       <c r="J295" s="2" t="s">
         <v>16</v>
@@ -11935,25 +11926,25 @@
         <v>9</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D296" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="E296" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="E296" s="2" t="s">
-        <v>622</v>
-      </c>
       <c r="F296" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>37.76</v>
+        <v>37.67</v>
       </c>
       <c r="J296" s="2" t="s">
         <v>16</v>
@@ -11964,28 +11955,28 @@
         <v>2023</v>
       </c>
       <c r="B297" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="D297" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="E297" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="E297" s="2" t="s">
-        <v>624</v>
-      </c>
       <c r="F297" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>37.67</v>
+        <v>37.54</v>
       </c>
       <c r="J297" s="2" t="s">
         <v>16</v>
@@ -11996,28 +11987,28 @@
         <v>2023</v>
       </c>
       <c r="B298" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D298" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="E298" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="E298" s="2" t="s">
-        <v>626</v>
-      </c>
       <c r="F298" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>37.54</v>
+        <v>37.5</v>
       </c>
       <c r="J298" s="2" t="s">
         <v>16</v>
@@ -12028,28 +12019,28 @@
         <v>2023</v>
       </c>
       <c r="B299" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>628</v>
+        <v>471</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H299" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>37.5</v>
+        <v>37.47</v>
       </c>
       <c r="J299" s="2" t="s">
         <v>16</v>
@@ -12060,28 +12051,28 @@
         <v>2023</v>
       </c>
       <c r="B300" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>474</v>
+        <v>628</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>37.47</v>
+        <v>37.46</v>
       </c>
       <c r="J300" s="2" t="s">
         <v>16</v>
@@ -12095,25 +12086,25 @@
         <v>9</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D301" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="E301" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="E301" s="2" t="s">
-        <v>631</v>
-      </c>
       <c r="F301" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>37.46</v>
+        <v>36.84</v>
       </c>
       <c r="J301" s="2" t="s">
         <v>16</v>
@@ -12124,28 +12115,28 @@
         <v>2023</v>
       </c>
       <c r="B302" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="D302" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="E302" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="E302" s="2" t="s">
-        <v>633</v>
-      </c>
       <c r="F302" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>36.84</v>
+        <v>36.82</v>
       </c>
       <c r="J302" s="2" t="s">
         <v>16</v>
@@ -12156,28 +12147,28 @@
         <v>2023</v>
       </c>
       <c r="B303" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C303" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E303" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="F303" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D303" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="E303" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="F303" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="G303" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>36.82</v>
+        <v>36.73</v>
       </c>
       <c r="J303" s="2" t="s">
         <v>16</v>
@@ -12188,28 +12179,28 @@
         <v>2023</v>
       </c>
       <c r="B304" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D304" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E304" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="E304" s="2" t="s">
-        <v>637</v>
-      </c>
       <c r="F304" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>36.73</v>
+        <v>36.61</v>
       </c>
       <c r="J304" s="2" t="s">
         <v>16</v>
@@ -12220,28 +12211,28 @@
         <v>2023</v>
       </c>
       <c r="B305" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D305" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="E305" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="E305" s="2" t="s">
-        <v>639</v>
-      </c>
       <c r="F305" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>36.61</v>
+        <v>36.43</v>
       </c>
       <c r="J305" s="2" t="s">
         <v>16</v>
@@ -12252,28 +12243,28 @@
         <v>2023</v>
       </c>
       <c r="B306" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D306" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E306" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="E306" s="2" t="s">
-        <v>641</v>
-      </c>
       <c r="F306" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>36.43</v>
+        <v>36.41</v>
       </c>
       <c r="J306" s="2" t="s">
         <v>16</v>
@@ -12284,28 +12275,28 @@
         <v>2023</v>
       </c>
       <c r="B307" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D307" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="E307" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="E307" s="2" t="s">
-        <v>643</v>
-      </c>
       <c r="F307" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>36.41</v>
+        <v>36.07</v>
       </c>
       <c r="J307" s="2" t="s">
         <v>16</v>
@@ -12319,25 +12310,25 @@
         <v>9</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D308" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E308" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="E308" s="2" t="s">
-        <v>645</v>
-      </c>
       <c r="F308" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>36.07</v>
+        <v>35.71</v>
       </c>
       <c r="J308" s="2" t="s">
         <v>16</v>
@@ -12348,28 +12339,28 @@
         <v>2023</v>
       </c>
       <c r="B309" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="D309" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="E309" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="E309" s="2" t="s">
-        <v>647</v>
-      </c>
       <c r="F309" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>35.71</v>
+        <v>35.66</v>
       </c>
       <c r="J309" s="2" t="s">
         <v>16</v>
@@ -12383,25 +12374,25 @@
         <v>10</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D310" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="E310" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="E310" s="2" t="s">
-        <v>649</v>
-      </c>
       <c r="F310" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>35.66</v>
+        <v>35.19</v>
       </c>
       <c r="J310" s="2" t="s">
         <v>16</v>
@@ -12415,25 +12406,25 @@
         <v>10</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D311" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="E311" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="E311" s="2" t="s">
-        <v>651</v>
-      </c>
       <c r="F311" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>35.19</v>
+        <v>34.81</v>
       </c>
       <c r="J311" s="2" t="s">
         <v>16</v>
@@ -12444,28 +12435,28 @@
         <v>2023</v>
       </c>
       <c r="B312" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D312" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E312" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="E312" s="2" t="s">
-        <v>653</v>
-      </c>
       <c r="F312" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>34.81</v>
+        <v>34.28</v>
       </c>
       <c r="J312" s="2" t="s">
         <v>16</v>
@@ -12476,28 +12467,28 @@
         <v>2023</v>
       </c>
       <c r="B313" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="D313" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="E313" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="E313" s="2" t="s">
-        <v>655</v>
-      </c>
       <c r="F313" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>34.28</v>
+        <v>34.2</v>
       </c>
       <c r="J313" s="2" t="s">
         <v>16</v>
@@ -12511,25 +12502,25 @@
         <v>10</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D314" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="E314" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="E314" s="2" t="s">
-        <v>657</v>
-      </c>
       <c r="F314" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>34.2</v>
+        <v>33.94</v>
       </c>
       <c r="J314" s="2" t="s">
         <v>16</v>
@@ -12540,28 +12531,28 @@
         <v>2023</v>
       </c>
       <c r="B315" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D315" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="E315" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="E315" s="2" t="s">
-        <v>659</v>
-      </c>
       <c r="F315" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>33.94</v>
+        <v>33.9</v>
       </c>
       <c r="J315" s="2" t="s">
         <v>16</v>
@@ -12572,28 +12563,28 @@
         <v>2023</v>
       </c>
       <c r="B316" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="D316" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="E316" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="E316" s="2" t="s">
-        <v>661</v>
-      </c>
       <c r="F316" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>33.9</v>
+        <v>33.46</v>
       </c>
       <c r="J316" s="2" t="s">
         <v>16</v>
@@ -12604,28 +12595,28 @@
         <v>2023</v>
       </c>
       <c r="B317" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D317" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="E317" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="E317" s="2" t="s">
-        <v>663</v>
-      </c>
       <c r="F317" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I317" s="2" t="n">
-        <v>33.46</v>
+        <v>33.17</v>
       </c>
       <c r="J317" s="2" t="s">
         <v>16</v>
@@ -12639,25 +12630,25 @@
         <v>9</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D318" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="E318" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="E318" s="2" t="s">
-        <v>665</v>
-      </c>
       <c r="F318" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>33.17</v>
+        <v>33.04</v>
       </c>
       <c r="J318" s="2" t="s">
         <v>16</v>
@@ -12668,28 +12659,28 @@
         <v>2023</v>
       </c>
       <c r="B319" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="D319" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="E319" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="E319" s="2" t="s">
-        <v>667</v>
-      </c>
       <c r="F319" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>33.04</v>
+        <v>32.99</v>
       </c>
       <c r="J319" s="2" t="s">
         <v>16</v>
@@ -12703,25 +12694,25 @@
         <v>10</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D320" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="E320" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="E320" s="2" t="s">
-        <v>669</v>
-      </c>
       <c r="F320" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>32.99</v>
+        <v>31.54</v>
       </c>
       <c r="J320" s="2" t="s">
         <v>16</v>
@@ -12735,25 +12726,25 @@
         <v>10</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D321" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="E321" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="E321" s="2" t="s">
-        <v>671</v>
-      </c>
       <c r="F321" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I321" s="2" t="n">
-        <v>31.54</v>
+        <v>30.89</v>
       </c>
       <c r="J321" s="2" t="s">
         <v>16</v>
@@ -12764,28 +12755,28 @@
         <v>2023</v>
       </c>
       <c r="B322" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D322" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="E322" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="E322" s="2" t="s">
-        <v>673</v>
-      </c>
       <c r="F322" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>30.89</v>
+        <v>27.68</v>
       </c>
       <c r="J322" s="2" t="s">
         <v>16</v>
@@ -12799,25 +12790,25 @@
         <v>9</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D323" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="E323" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="E323" s="2" t="s">
-        <v>675</v>
-      </c>
       <c r="F323" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>27.68</v>
+        <v>25.06</v>
       </c>
       <c r="J323" s="2" t="s">
         <v>16</v>
@@ -12828,67 +12819,35 @@
         <v>2023</v>
       </c>
       <c r="B324" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="D324" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="E324" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="E324" s="2" t="s">
-        <v>677</v>
-      </c>
       <c r="F324" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>25.06</v>
+        <v>24.53</v>
       </c>
       <c r="J324" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="325">
-      <c r="A325" s="2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B325" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C325" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="D325" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="E325" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="F325" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="G325" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="H325" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I325" s="2" t="n">
-        <v>24.53</v>
-      </c>
-      <c r="J325" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J325"/>
+  <autoFilter ref="A1:J324"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -12905,7 +12864,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -12913,50 +12872,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
   </sheetData>
@@ -12978,21 +12937,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13001,7 +12960,7 @@
         <v>2023</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2023.xlsx
@@ -2056,7 +2056,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:54</t>
+    <t xml:space="preserve">2026-09-08 10:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
